--- a/fase_2/precios/lista_botas_26_27.xlsx
+++ b/fase_2/precios/lista_botas_26_27.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="8">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="9">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1710</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="10">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1880</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="11">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="13">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1620</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="14">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1620</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="15">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1310</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="16">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1620</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="17">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1620</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="18">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1310</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="19">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1310</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="20">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1310</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="21">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1310</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="22">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1310</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="23">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1310</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="24">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1100</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="25">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="26">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="27">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1220</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="28">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1310</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="29">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="30">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="31">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="32">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="33">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="34">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="35">
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="36">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="37">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="38">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1800</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="39">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1800</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="40">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2880</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="41">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2470</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="42">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2970</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="43">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3070</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="44">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2470</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="45">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="50">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2010</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="52">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2940</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="53">
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="54">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="65">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="66">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="67">
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="68">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="69">
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1490</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="70">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1490</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="71">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1490</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="72">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1920</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="73">
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1310</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="74">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="75">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="76">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="77">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="78">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="79">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="80">
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="84">
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1470</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="93">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1470</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="94">
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="95">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="97">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="98">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="99">
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="100">
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1350</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="101">
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="102">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="103">
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1530</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="104">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="105">
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="106">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1620</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="107">
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1620</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="108">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="109">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="110">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="111">
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="112">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="113">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="114">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="115">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="117">
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="118">
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="122">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="124">
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="128">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="130">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2650</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="133">
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1710</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="138">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="142">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="143">
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="144">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1110</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="145">
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1110</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="146">
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="149">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>1350</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="153">
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1490</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="154">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1490</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="155">
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="156">
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>3550</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="167">
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>3550</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="168">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="173">
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="174">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>1240</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="175">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="176">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="177">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="178">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="179">
@@ -2205,7 +2205,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="180">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="181">
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>1240</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="182">
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="183">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="184">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="185">
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>1220</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="188">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>1220</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="189">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>1220</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="190">
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>1220</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="191">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>1220</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="192">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="193">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="194">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="195">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>1240</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="196">
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>1220</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="197">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="201">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="202">
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="203">
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="204">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="205">
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="206">
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>1350</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="207">
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>1350</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="208">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="209">
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="210">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>1350</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="211">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="212">
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>1350</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="213">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="214">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>1220</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="215">
@@ -2565,7 +2565,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>1220</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="216">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="220">
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="221">
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>2010</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="222">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>1350</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="223">
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>1220</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="224">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>1310</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="225">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>1310</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="226">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="227">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>1240</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="228">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>1220</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="230">
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="231">
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="233">
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="234">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1270</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="236">
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1270</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="237">
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1530</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="238">
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>1530</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="239">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="240">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="241">
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="242">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="243">
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="244">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="245">
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>1240</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="246">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>1240</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="247">
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="248">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="249">
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>1240</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="250">
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="251">
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="252">
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="253">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="256">
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="257">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="259">
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>1350</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="263">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="264">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>1350</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="265">
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>1530</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="266">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>1550</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="267">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>1550</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="268">
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>1530</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="269">
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>1530</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="270">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>1490</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="271">
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="272">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>1310</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="273">
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="274">
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="275">
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="276">
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>1800</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="277">
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="278">
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="279">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="280">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="281">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="282">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="283">
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>1350</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="284">
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="285">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="286">
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="287">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>1530</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="288">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>1490</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="289">
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="290">
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="291">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="292">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="293">
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="294">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="297">
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="303">
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="332">
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="352">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="358">
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>1350</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="372">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="373">
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>1310</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="374">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>1310</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="375">
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="376">
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="383">
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="386">
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="387">
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="388">
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>1310</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="389">
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="390">
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>2510</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="393">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>1490</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="394">
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>1310</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="401">
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>1310</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="402">
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>2100</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="403">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>2100</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="404">
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>2100</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="405">
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="410">
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="411">
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>2100</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="412">
@@ -4535,7 +4535,7 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>2130</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="413">
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="416">
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>1920</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="417">
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>2060</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="418">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>2210</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="419">
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="420">
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>1240</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="421">
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="422">
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>1240</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="423">
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>3600</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="424">
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>3820</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="425">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>3290</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="426">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>1310</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="427">
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>1910</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="428">
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>2360</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="429">
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>1840</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="430">
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>1990</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="431">
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>1910</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="432">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>1990</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="433">
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>1990</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="434">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>1740</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="435">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>1740</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="436">
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>1910</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="437">
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>1910</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="438">
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>1350</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="439">
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="440">
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="441">
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>1110</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="442">
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>1560</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="446">
@@ -4875,7 +4875,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>1560</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="447">
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>1560</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="448">
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>1560</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="449">
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="450">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>1400</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="451">
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>1400</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="452">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>1420</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="457">
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>1420</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="458">
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="459">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>1420</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="460">
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>1420</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="461">
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>1490</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="462">
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="463">
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>1530</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="464">
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>1490</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="465">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>1490</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="466">
@@ -5075,7 +5075,7 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>1350</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="467">
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>1400</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="468">
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="469">
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>1560</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="470">
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="471">
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="472">
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="473">
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>1350</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="474">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>1400</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="475">
@@ -5165,7 +5165,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="476">
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="477">
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="478">
@@ -5195,7 +5195,7 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>1490</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="479">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="480">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="481">
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>1490</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="482">
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="483">
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>1490</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="484">
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>1310</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="485">
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="486">
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="487">
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>710</v>
+        <v>700</v>
       </c>
     </row>
     <row r="488">
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="489">
@@ -5355,7 +5355,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
     </row>
     <row r="495">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
     </row>
     <row r="496">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="501">
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>690</v>
+        <v>680</v>
       </c>
     </row>
     <row r="512">
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>690</v>
+        <v>680</v>
       </c>
     </row>
     <row r="513">
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>710</v>
+        <v>700</v>
       </c>
     </row>
     <row r="514">
@@ -5555,7 +5555,7 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>710</v>
+        <v>700</v>
       </c>
     </row>
     <row r="515">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>710</v>
+        <v>700</v>
       </c>
     </row>
     <row r="517">
@@ -5605,7 +5605,7 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>570</v>
+        <v>560</v>
       </c>
     </row>
     <row r="520">
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>570</v>
+        <v>560</v>
       </c>
     </row>
     <row r="521">
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>570</v>
+        <v>560</v>
       </c>
     </row>
     <row r="522">
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>620</v>
+        <v>610</v>
       </c>
     </row>
     <row r="523">
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>1110</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="532">
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>710</v>
+        <v>700</v>
       </c>
     </row>
     <row r="534">
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>710</v>
+        <v>700</v>
       </c>
     </row>
     <row r="535">
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>660</v>
+        <v>650</v>
       </c>
     </row>
     <row r="536">
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>660</v>
+        <v>650</v>
       </c>
     </row>
     <row r="537">
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>710</v>
+        <v>700</v>
       </c>
     </row>
     <row r="538">
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
     </row>
     <row r="539">
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
     </row>
     <row r="540">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
     </row>
     <row r="541">
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
     </row>
     <row r="542">
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>570</v>
+        <v>560</v>
       </c>
     </row>
     <row r="543">
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
     </row>
     <row r="544">
@@ -5855,7 +5855,7 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
     </row>
     <row r="545">
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="548">
@@ -5895,7 +5895,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="549">
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="550">
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>710</v>
+        <v>700</v>
       </c>
     </row>
     <row r="556">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>660</v>
+        <v>650</v>
       </c>
     </row>
     <row r="559">
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>620</v>
+        <v>610</v>
       </c>
     </row>
     <row r="561">
@@ -6025,7 +6025,7 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
     </row>
     <row r="562">
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>480</v>
+        <v>470</v>
       </c>
     </row>
     <row r="563">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
     </row>
     <row r="568">
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
     </row>
     <row r="569">
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
     </row>
     <row r="570">
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>710</v>
+        <v>700</v>
       </c>
     </row>
     <row r="571">
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>1150</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="577">
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="585">
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="599">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>1170</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="609">
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="610">
@@ -6515,7 +6515,7 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="611">
@@ -6525,7 +6525,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="612">
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>620</v>
+        <v>610</v>
       </c>
     </row>
     <row r="617">
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>710</v>
+        <v>700</v>
       </c>
     </row>
     <row r="634">
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>660</v>
+        <v>650</v>
       </c>
     </row>
     <row r="636">
@@ -6775,7 +6775,7 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>660</v>
+        <v>650</v>
       </c>
     </row>
     <row r="637">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>570</v>
+        <v>560</v>
       </c>
     </row>
     <row r="639">
@@ -6805,7 +6805,7 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>1110</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="640">
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
     </row>
     <row r="646">
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>620</v>
+        <v>610</v>
       </c>
     </row>
     <row r="647">
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="649">
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="650">
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>600</v>
+        <v>590</v>
       </c>
     </row>
     <row r="651">
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>600</v>
+        <v>590</v>
       </c>
     </row>
     <row r="652">
@@ -6935,7 +6935,7 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>620</v>
+        <v>610</v>
       </c>
     </row>
     <row r="653">
@@ -6945,7 +6945,7 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>660</v>
+        <v>650</v>
       </c>
     </row>
     <row r="654">
@@ -6955,7 +6955,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>660</v>
+        <v>650</v>
       </c>
     </row>
     <row r="655">
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="656">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
     </row>
     <row r="657">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="658">
@@ -6995,7 +6995,7 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="659">
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
     </row>
     <row r="660">
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
     </row>
     <row r="661">
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
     </row>
     <row r="662">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
     </row>
     <row r="663">
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
     </row>
     <row r="667">
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>710</v>
+        <v>700</v>
       </c>
     </row>
     <row r="674">
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
     </row>
     <row r="675">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="676">
@@ -7185,7 +7185,7 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>710</v>
+        <v>700</v>
       </c>
     </row>
     <row r="678">
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="679">
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>660</v>
+        <v>650</v>
       </c>
     </row>
     <row r="682">
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>710</v>
+        <v>700</v>
       </c>
     </row>
     <row r="683">
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>710</v>
+        <v>700</v>
       </c>
     </row>
     <row r="684">
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
     </row>
     <row r="685">
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
     </row>
     <row r="686">
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>480</v>
+        <v>470</v>
       </c>
     </row>
     <row r="688">
